--- a/clients/drwu/website-renewal-2026/DR.WU_website-renewal-2026_03-04-06.xlsx
+++ b/clients/drwu/website-renewal-2026/DR.WU_website-renewal-2026_03-04-06.xlsx
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>現行ページ階層の棚卸し＋改修意向を反映した改修後の構成。第1階層セルの色は既存/新設/レガシーの区分を示す。</t>
+          <t>現行ページ階層の棚卸し＋改修意向を反映した改修後の構成（定期便/マイページ/フォーム一体型LP追加を含む）。第1階層セルの色は既存/新設/レガシーの区分を示す。</t>
         </is>
       </c>
     </row>
@@ -1861,71 +1861,71 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>SUBSCRIPTION(新設・定期便)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>マンデリック定期便</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr"/>
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>/products/mandelic-intensive-renewal-serum（既存商品ページを拡張）</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>対象商品にサブスクリプション購入オプションを追加</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>要確認(アプリ側の商品登録要否)</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>商品ページ拡張＋アプリ連携</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>都度購入に加えて定期便(サブスクリプション)購入を選択可能にする。お届け周期・定期便割引を設定</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>アプリ未選定(ハックリベリー「定期購買」／Mikawaya Subscription)。SERIESのマンデリック特設LP(既存行)とも連携</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>新規追加要件(FR-12)。マイページの定期便管理(MYPAGE参照)とセットで機能する</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>CATEGORY(カテゴリから探す・既存)</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>洗顔</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr"/>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>/collections/facewashing</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>既存SKU</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H33" s="7" t="inlineStr">
-        <is>
-          <t>コレクション</t>
-        </is>
-      </c>
-      <c r="I33" s="7" t="inlineStr">
-        <is>
-          <t>現状維持</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>TOP露出はCONCERN/SERIES優先に縮小、ナビには残す</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="inlineStr">
-        <is>
-          <t>既存ページ</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>CATEGORY(既存)</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>化粧水</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr"/>
       <c r="D34" s="7" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>/collections/toner</t>
+          <t>/collections/facewashing</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>TOP露出はCONCERN/SERIES優先に縮小、ナビには残す</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>美容液</t>
+          <t>化粧水</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr"/>
       <c r="D35" s="7" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>/collections/美容液</t>
+          <t>/collections/toner</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2016,14 +2016,14 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>フェイスマスク</t>
+          <t>美容液</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr"/>
       <c r="D36" s="7" t="inlineStr"/>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>/collections/mask</t>
+          <t>/collections/美容液</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -2057,7 +2057,7 @@
         </is>
       </c>
     </row>
-    <row r="37" ht="22" customHeight="1">
+    <row r="37" ht="18" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
           <t>CATEGORY(既存)</t>
@@ -2065,14 +2065,14 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>ベースメイク</t>
+          <t>フェイスマスク</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="7" t="inlineStr"/>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>/collections/basemake</t>
+          <t>/collections/mask</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>SERIESのベースメイクと同一。ナビ表記統一を提案</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
@@ -2106,7 +2106,7 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="18" customHeight="1">
+    <row r="38" ht="22" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>CATEGORY(既存)</t>
@@ -2114,137 +2114,145 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>全製品一覧</t>
+          <t>ベースメイク</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr"/>
       <c r="D38" s="7" t="inlineStr"/>
       <c r="E38" s="7" t="inlineStr">
         <is>
+          <t>/collections/basemake</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>既存SKU</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>コレクション</t>
+        </is>
+      </c>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>現状維持</t>
+        </is>
+      </c>
+      <c r="J38" s="7" t="inlineStr">
+        <is>
+          <t>SERIESのベースメイクと同一。ナビ表記統一を提案</t>
+        </is>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>既存ページ</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>CATEGORY(既存)</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>全製品一覧</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr"/>
+      <c r="D39" s="7" t="inlineStr"/>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
           <t>/collections/all</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>全SKU</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>コレクション</t>
         </is>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>現状維持</t>
         </is>
       </c>
-      <c r="J38" s="7" t="inlineStr"/>
-      <c r="K38" s="7" t="inlineStr">
+      <c r="J39" s="7" t="inlineStr"/>
+      <c r="K39" s="7" t="inlineStr">
         <is>
           <t>既存ページ</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>GUIDE(使い方ガイド)</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr"/>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr"/>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>ご利用ガイド</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>/pages/ご利用ガイド</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr"/>
-      <c r="G39" s="5" t="inlineStr"/>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>既存の利用ガイド内容</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr"/>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>既存ページ</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>GUIDE(新設)</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr"/>
-      <c r="C40" s="6" t="inlineStr"/>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr"/>
+      <c r="C41" s="6" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>マンデリック使い方ガイド</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>/pages/mandelic-guide（新設）</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>ページ</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>角質ケアの使用頻度・保湿方法・よくある不安へのQ&amp;A</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>新規制作</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>改修方針⑦</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>LINE(新設)</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>LINE公式・30日集中プログラム</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr"/>
-      <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>/pages/line-program（新設）</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -2256,348 +2264,388 @@
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>LINE友だち登録導線＋「つるん肌30日集中プログラム」の説明</t>
+          <t>角質ケアの使用頻度・保湿方法・よくある不安へのQ&amp;A</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Shopify連携アプリ＋LINE公式アカウントとの連携、購入者への自動配信構築が前提</t>
+          <t>新規制作</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>改修方針⑦⑧</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="34" customHeight="1">
+          <t>改修方針⑦</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>MEMBER(新設・会員ロイヤリティ)</t>
+          <t>LINE(新設)</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>会員登録・ログイン</t>
+          <t>LINE公式・30日集中プログラム</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>/account/register</t>
+          <t>/pages/line-program（新設）</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr"/>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Shopify標準機能</t>
+          <t>ページ</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>LINE連携登録・ポイントプレゼントに刷新</t>
+          <t>LINE友だち登録導線＋「つるん肌30日集中プログラム」の説明</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>CRM PLUS on LINE等アプリ導入が前提</t>
+          <t>Shopify連携アプリ＋LINE公式アカウントとの連携、購入者への自動配信構築が前提</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>改修方針⑧。既存ログイン(/customer_authentication/redirect)を置き換え</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="18" customHeight="1">
+          <t>改修方針⑦⑧</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="34" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>MEMBER(新設)</t>
+          <t>MEMBER(新設・会員ロイヤリティ)</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>ポイントプログラム説明</t>
+          <t>会員登録・ログイン</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>/pages/points（新設）</t>
+          <t>/account/register</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr"/>
       <c r="H43" s="6" t="inlineStr">
         <is>
+          <t>Shopify標準機能</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>LINE連携登録・ポイントプレゼントに刷新</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>CRM PLUS on LINE等アプリ導入が前提</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>改修方針⑧。既存ログイン(/customer_authentication/redirect)を置き換え</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>MEMBER(新設)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>ポイントプログラム説明</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr"/>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>/pages/points（新設）</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="I43" s="6" t="inlineStr">
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>ポイント付与ルール・誕生日特典の説明</t>
         </is>
       </c>
-      <c r="J43" s="6" t="inlineStr"/>
-      <c r="K43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="38" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>MYPAGE(新設)</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>マイページ</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr"/>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>トップ</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>/account（拡張）</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t>Shopify標準機能を拡張</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>注文履歴・定期便管理・ポイント管理・会員情報をタブ構成でまとめる</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>定期便機能(SUBSCRIPTION)の追加に伴い新規発生した要件。既存の会員登録/ポイント説明ページとは別に、実際の管理画面として新設</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>新規追加要件(FR-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>MYPAGE(新設)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>マイページ</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>定期便管理</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>/account（拡張）</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t>アプリ連携(顧客ポータル埋め込み)</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>次回お届け日変更・商品変更・スキップ・解約</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>定期便アプリ(ハックリベリー/Mikawaya)の顧客ポータル機能をマイページに埋め込み、またはリンクする方式を想定</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>新規追加要件(FR-12, FR-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>MYPAGE(新設)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>マイページ</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr"/>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>ポイント管理</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>/account（拡張）</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t>アプリ連携(ポイントAPI)</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>ポイント残高・獲得履歴・獲得予定ポイントの確認</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>F-11のLINE連携アプリ(CRM PLUS on LINE/StoreCRM)のポイントAPIを利用</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>新規追加要件(FR-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="46" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>CHATBOT-LP(新設)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>フォーム一体型LP</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr"/>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>マンデリック(チャットボット購入)</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>/pages/mandelic-chat-lp（新設）</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>対象はマンデリックのみ想定</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr">
+        <is>
+          <t>アプリ(テーマ拡張)</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>広告流入向け。チャット形式の会話UIで商品選択〜連絡先〜配送先入力を完結し、標準決済ページへ自動反映</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Shopifyはフォーム一体型LPを直接実装できないための代替方式。想定候補: シンプルフォーム一体型LP｜お手軽チャットボット購入(株式会社UnReact、月額$49.99〜)</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>新規追加要件(FR-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>COLUMN(コラム/NOTE)</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>コラム一覧</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr"/>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>/blogs/column</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr"/>
-      <c r="G44" s="4" t="inlineStr"/>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>ブログ一覧</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>スキンケア解説／美容ホロスコープ／台湾文化など18本以上が混在</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>カテゴリタグでの絞り込みUIを追加提案</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>改修方針⑨</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>COLUMN</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr"/>
-      <c r="C45" s="5" t="inlineStr"/>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>個別記事(既存多数)</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>/blogs/column/*</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>ブログ記事</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>既存記事群(drwu-skincarecolumn1〜11、beauty-horoscope等)</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>既存ページ</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>お問い合わせ</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr"/>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>/pages/contact</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="inlineStr"/>
-      <c r="G46" s="4" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>ページ</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>現状維持</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>既存ページ</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>よくあるご質問</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr"/>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>/pages/drwu-jp-faq</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>ページ</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>現状維持</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>既存ページ</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>プライバシーポリシー</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr"/>
-      <c r="D48" s="4" t="inlineStr"/>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>/policies/privacy-policy</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>ポリシーページ</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>現状維持</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr"/>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>既存ページ</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>特定商取引法に基づく表記</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="5" t="inlineStr"/>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>/policies/legal-notice</t>
+          <t>/blogs/column</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr"/>
       <c r="G49" s="5" t="inlineStr"/>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>ポリシーページ</t>
+          <t>ブログ一覧</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>現状維持</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr"/>
+          <t>スキンケア解説／美容ホロスコープ／台湾文化など18本以上が混在</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>カテゴリタグでの絞り込みUIを追加提案</t>
+        </is>
+      </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>既存ページ</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="18" customHeight="1">
+          <t>改修方針⑨</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>SUPPORT</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>検索・カート</t>
-        </is>
-      </c>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr"/>
       <c r="C50" s="4" t="inlineStr"/>
-      <c r="D50" s="4" t="inlineStr"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>個別記事(既存多数)</t>
+        </is>
+      </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>/search, /cart</t>
+          <t>/blogs/column/*</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
       <c r="G50" s="4" t="inlineStr"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Shopify標準機能</t>
+          <t>ブログ記事</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>現状維持</t>
+          <t>既存記事群(drwu-skincarecolumn1〜11、beauty-horoscope等)</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr"/>
@@ -2607,99 +2655,284 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="86" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>お問い合わせ</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>/pages/contact</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>現状維持</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>既存ページ</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>よくあるご質問</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>/pages/drwu-jp-faq</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>現状維持</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>既存ページ</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>プライバシーポリシー</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>/policies/privacy-policy</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr"/>
+      <c r="G53" s="5" t="inlineStr"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>ポリシーページ</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>現状維持</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr"/>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>既存ページ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>特定商取引法に基づく表記</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr"/>
+      <c r="D54" s="4" t="inlineStr"/>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>/policies/legal-notice</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>ポリシーページ</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>現状維持</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>既存ページ</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="18" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>SUPPORT</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>検索・カート</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>/search, /cart</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr"/>
+      <c r="G55" s="5" t="inlineStr"/>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Shopify標準機能</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>現状維持</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr"/>
+      <c r="K55" s="5" t="inlineStr">
+        <is>
+          <t>既存ページ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="86" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
         <is>
           <t>レガシー・要整理</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B56" s="8" t="inlineStr">
         <is>
           <t>過去キャンペーン系コレクション</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr"/>
-      <c r="D51" s="8" t="inlineStr"/>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr"/>
+      <c r="D56" s="8" t="inlineStr"/>
+      <c r="E56" s="8" t="inlineStr">
         <is>
           <t>/collections/happybox2023, /collections/2020年-ベストコスメ受賞, /collections/2021-2022-special-set, /collections/20251114-17, /collections/line限定セット, /collections/great-deal, /collections/trial 他</t>
         </is>
       </c>
-      <c r="F51" s="8" t="inlineStr">
+      <c r="F56" s="8" t="inlineStr">
         <is>
           <t>既存SKU(終了済み含む)</t>
         </is>
       </c>
-      <c r="G51" s="8" t="inlineStr">
+      <c r="G56" s="8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="H51" s="8" t="inlineStr">
+      <c r="H56" s="8" t="inlineStr">
         <is>
           <t>コレクション(旧)</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>終了済みキャンペーンの残存コレクション</t>
         </is>
       </c>
-      <c r="J51" s="8" t="inlineStr">
+      <c r="J56" s="8" t="inlineStr">
         <is>
           <t>非表示化または301リダイレクトでの整理を提案。有効情報はCAMPAIGN/SET階層へ移管</t>
         </is>
       </c>
-      <c r="K51" s="8" t="inlineStr">
+      <c r="K56" s="8" t="inlineStr">
         <is>
           <t>課題③に対応。sitemap上52コレクション中、現行グローバルナビ非掲載分が棚卸し対象</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="50" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
+    <row r="57" ht="50" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
         <is>
           <t>レガシー・要整理</t>
         </is>
       </c>
-      <c r="B52" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>シリーズコレクションの重複</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr"/>
-      <c r="D52" s="8" t="inlineStr"/>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr"/>
+      <c r="D57" s="8" t="inlineStr"/>
+      <c r="E57" s="8" t="inlineStr">
         <is>
           <t>/collections/sunscreen, /collections/sunscreen-series, /collections/sunscreen-suncare-system 他</t>
         </is>
       </c>
-      <c r="F52" s="8" t="inlineStr">
+      <c r="F57" s="8" t="inlineStr">
         <is>
           <t>既存SKU</t>
         </is>
       </c>
-      <c r="G52" s="8" t="inlineStr">
+      <c r="G57" s="8" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
         <is>
           <t>コレクション(旧)</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>同一シリーズに対し複数コレクションが並存</t>
         </is>
       </c>
-      <c r="J52" s="8" t="inlineStr">
+      <c r="J57" s="8" t="inlineStr">
         <is>
           <t>1シリーズ1コレクションへの正規化を提案</t>
         </is>
       </c>
-      <c r="K52" s="8" t="inlineStr">
+      <c r="K57" s="8" t="inlineStr">
         <is>
           <t>SERIES階層のUVコレクションに統合</t>
         </is>
@@ -2720,7 +2953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2743,7 +2976,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SCR-01〜SCR-22。区分列の色が既存/新設/レガシーに対応。「ワイヤーフレーム対象」列は05成果物との対応関係を示す。</t>
+          <t>SCR-01〜SCR-26。区分列の色が既存/新設/レガシーに対応。「ワイヤーフレーム対象」列は05成果物との対応関係を示す（SCR-23〜26は追加候補・未着手）。</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3484,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="34" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>SCR-12</t>
@@ -3264,7 +3497,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>既存</t>
+          <t>既存拡張</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -3279,7 +3512,7 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>FR-04, FR-06</t>
+          <t>FR-04, FR-06, FR-12</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -3289,7 +3522,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>全SKU共通のShopify標準商品ページテンプレート</t>
+          <t>全SKU共通のShopify標準商品ページテンプレート。マンデリック等対象商品には定期便購入オプションを追加</t>
         </is>
       </c>
     </row>
@@ -3710,6 +3943,174 @@
       <c r="H25" s="8" t="inlineStr">
         <is>
           <t>非表示化または301リダイレクトの対象。ワイヤーフレーム不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>SCR-23</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>マイページ トップ</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>MYPAGE(新設)</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>/account（拡張）</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>FR-13</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>追加候補(未着手)</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>注文履歴・定期便管理・ポイント管理・会員情報のタブ構成。定期便機能の追加に伴い新設</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>SCR-24</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>マイページ内 定期便管理タブ</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>MYPAGE(新設)</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>/account（拡張）</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>FR-12, FR-13</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>追加候補(未着手)</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>次回お届け日変更・商品変更・スキップ・解約。定期便アプリの顧客ポータルを埋め込み想定</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="34" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>SCR-25</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>マイページ内 ポイント管理タブ</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>MYPAGE(新設)</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>/account（拡張）</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>FR-13</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>追加候補(未着手)</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>ポイント残高・獲得履歴・獲得予定の確認。既存のポイントプログラム説明ページ(SCR-16)とは別で、実残高を見る画面</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>SCR-26</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>フォーム一体型LP(チャットボット購入・マンデリック)</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>新設</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>CHATBOT-LP(新設)</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>/pages/mandelic-chat-lp（新設）</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>FR-14</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>追加候補(未着手)</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>広告流入向け。チャット形式で商品選択〜連絡先〜配送先入力を完結し決済ページへ自動反映</t>
         </is>
       </c>
     </row>
@@ -3728,7 +4129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3752,7 +4153,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>F-01〜F-14。分類列の色がShopify標準/Shopifyアプリ/独自開発に対応。優先度はMust(濃)/Should/Could(淡)の階調で表現。</t>
+          <t>F-01〜F-18。分類列の色がShopify標準/Shopifyアプリ/独自開発に対応。優先度はMust(濃)/Should/Could(淡)の階調で表現。</t>
         </is>
       </c>
     </row>
@@ -4434,6 +4835,194 @@
       <c r="I17" s="10" t="inlineStr">
         <is>
           <t>06の非機能要件・計測要件とセット</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>F-15</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>定期便(サブスクリプション)購入機能</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Shopifyアプリ</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>FR-12</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>SCR-12,SCR-24</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>対象商品(マンデリック等)の商品ページに定期便購入オプションを追加。お届け周期・割引の設定を行う</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>ハックリベリー「定期購買」 または Mikawaya Subscription(要選定。06参照)</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>新規追加要件。商品ページ(SCR-12)の改修を伴う</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>F-16</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>マイページ 定期便管理タブ</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>独自開発(テーマ拡張)+アプリ連携</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>FR-13</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>SCR-23,SCR-24</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>マイページ内で次回お届け日変更・商品変更・スキップ・解約を行えるようにする</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>F-15の定期便アプリが提供する顧客ポータルをマイページに埋め込み or リンク</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>定期便アプリの顧客ポータル機能の有無・カスタマイズ可否に実装方式が依存</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>F-17</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>マイページ ポイント管理タブ</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>独自開発(テーマ拡張)+アプリ連携</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>FR-13</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>SCR-23,SCR-25</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>マイページ内でポイント残高・獲得履歴・獲得予定ポイントを確認できるようにする</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>F-11と同一のLINE連携アプリ(CRM PLUS on LINE/StoreCRM)のポイントAPIを利用</t>
+        </is>
+      </c>
+      <c r="H20" s="11" t="inlineStr">
+        <is>
+          <t>Must</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>F-11(ポイント・ロイヤリティプログラム)の表示面をマイページに統合する位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>F-18</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>フォーム一体型LP/チャットボット購入(マンデリック)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Shopifyアプリ</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>FR-14</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>SCR-26</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>広告流入向けLPで、チャット形式の会話UIにより商品選択〜連絡先〜配送先入力を完結させ、標準決済ページへ自動反映する</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>シンプルフォーム一体型LP｜お手軽チャットボット購入(株式会社UnReact、月額$49.99〜、7日間無料体験)</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>Should</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Shopifyはフォーム一体型LPを直接実装できないための代替方式。他のLPビルダー(PageFly/EComposer等)も比較候補</t>
         </is>
       </c>
     </row>
@@ -4452,7 +5041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4744,167 +5333,201 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>ハックリベリー「定期購買」</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>定期便（サブスクリプション）購入機能</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>FR-12 / F-15, F-16</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>双方向（商品・顧客・お届けスケジュール）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>Shopify App連携（OAuth）</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>アプリ次第（要見積）</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>案A。国内実績の多い定期購買アプリ</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Mikawaya Subscription</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>定期便（サブスクリプション）購入機能（代替案）</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>FR-12 / F-15, F-16</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Shopify App連携（OAuth）</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>アプリ次第（要見積）</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>案B。ハックリベリーと比較の上で選定</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>シンプルフォーム一体型LP｜お手軽チャットボット購入（UnReact）</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>フォーム一体型LPのチャットボット購入代替実装</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>FR-14 / F-18</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>入力データを標準決済ページへ自動反映</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>Shopify App連携（テーマ拡張）</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>月額$49.99〜（年払い17%割引）、7日間無料体験</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Shopifyはフォーム一体型LPを直接実装できないための代替案</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>② データ設計（概要）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>・顧客(Customer) ── LINE友だちID（連携アプリ経由）／ポイント残高／注文履歴(Order)／会員ステータス（新規・継続・誕生日）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>・商品(Product) ── シリーズタグ（マンデリック/ヒアルコンプレクス/…）／悩みタグ（毛穴/乾燥/くすみ/ハリ/敏感肌/UV、複数付与可）／セット構成（バンドルアプリ側で単品⇄セットを保持）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>・キャンペーン(Campaign) ── 種別（初回限定/LINE特典/セット特典/季節企画）、掲載期間</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
+          <t>・顧客(Customer) ── LINE友だちID（連携アプリ経由）／ポイント残高／注文履歴(Order)／会員ステータス（新規・継続・誕生日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>・商品(Product) ── シリーズタグ（マンデリック/ヒアルコンプレクス/…）／悩みタグ（毛穴/乾燥/くすみ/ハリ/敏感肌/UV、複数付与可）／セット構成（バンドルアプリ側で単品⇄セットを保持）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>・キャンペーン(Campaign) ── 種別（初回限定/LINE特典/セット特典/季節企画）、掲載期間</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
           <t>・前提：現行商品には「シリーズ」分類はあるが「悩み」分類がないため、FR-03実装には商品タグの新規設計・全SKUへの付与が必要</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>・顧客(Customer) に定期便契約(Subscription)を追加 ── お届け周期・次回お届け日・スキップ/解約状態（定期便アプリ側で保持し、マイページから参照・操作）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>③ 非機能要件</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>要件</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>パフォーマンス</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>TOPページのセクション数増加後も表示速度（Core Web Vitals）を現状同等以上に維持する</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>画像の遅延読み込み・セクションの段階描画を検討</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>計測</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>TOP各セクション(①〜⑧)でのクリック率・コンバージョンをGA4イベントで取得できること</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>F-14。改善のPDCAに必須</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>SEO</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>コレクション統廃合・URL変更時は301リダイレクトで既存の評価を継承する</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>FR-11。レガシーコレクション整理時に必須</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>セキュリティ・個人情報保護</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>LINE連携・会員登録で扱う個人情報を適切に管理する</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>プライバシーポリシーの記載更新を伴う</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>可用性</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Shopifyプラットフォームおよび導入アプリのSLAに準拠する</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>自社での特別な可用性対策は行わない</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr"/>
@@ -4912,20 +5535,20 @@
       <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr"/>
     </row>
-    <row r="26" ht="26" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>保守性</t>
+          <t>計測</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>キャンペーンバナー・コラム・使い方ガイド等は運用担当者が更新できること</t>
+          <t>TOP各セクション(①〜⑧)でのクリック率・コンバージョンをGA4イベントで取得できること</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Shopify標準ページ/メタフィールドでの運用が基本方針</t>
+          <t>F-14。改善のPDCAに必須</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
@@ -4933,20 +5556,20 @@
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr"/>
     </row>
-    <row r="27" ht="22" customHeight="1">
+    <row r="27" ht="26" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>拡張性</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>将来的な多言語対応・海外展開を著しく阻害しない設計とする</t>
+          <t>コレクション統廃合・URL変更時は301リダイレクトで既存の評価を継承する</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>対象外事項だが設計時に配慮</t>
+          <t>FR-11。レガシーコレクション整理時に必須</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr"/>
@@ -4957,17 +5580,17 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>アクセシビリティ</t>
+          <t>セキュリティ・個人情報保護</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>主要導線はスマートフォンでの操作性を優先して設計する</t>
+          <t>LINE連携・会員登録で扱う個人情報を適切に管理する</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>ターゲットユーザーの主要デバイスを想定</t>
+          <t>プライバシーポリシーの記載更新を伴う</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
@@ -4975,57 +5598,158 @@
       <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr"/>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>可用性</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Shopifyプラットフォームおよび導入アプリのSLAに準拠する</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>自社での特別な可用性対策は行わない</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>保守性</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>キャンペーンバナー・コラム・使い方ガイド等は運用担当者が更新できること</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Shopify標準ページ/メタフィールドでの運用が基本方針</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>拡張性</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>将来的な多言語対応・海外展開を著しく阻害しない設計とする</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>対象外事項だが設計時に配慮</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>アクセシビリティ</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>主要導線はスマートフォンでの操作性を優先して設計する</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>ターゲットユーザーの主要デバイスを想定</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>④ 未確定事項（要すり合わせ）</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>・LINE連携アプリの最終選定（CRM PLUS on LINE／StoreCRM）と、対象ID数に応じたコスト試算</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>・バンドル/セット販売アプリの選定と在庫連動方式</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>・ランキングの集計方式（アプリ自動集計／運用者による手動更新）</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>・GA4の導入状況・既存の計測設計の有無</t>
         </is>
       </c>
     </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>・定期便アプリの最終選定（ハックリベリー「定期購買」／Mikawaya Subscription）と、顧客ポータル機能のマイページ埋め込み可否</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>・チャットボット購入アプリの最終選定（シンプルフォーム一体型LP／他のLPビルダー）と対象商品範囲（マンデリックのみか拡大するか）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A33:G33"/>
+  <mergeCells count="17">
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
